--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_wmprob.vois.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_wmprob.vois.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -234,13 +235,13 @@
         <v>24</v>
       </c>
       <c r="D3" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="0">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -254,13 +255,13 @@
         <v>25</v>
       </c>
       <c r="D4" s="0">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -274,13 +275,13 @@
         <v>26</v>
       </c>
       <c r="D5" s="0">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>35</v>
       </c>
       <c r="F5" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -294,13 +295,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="0">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -314,13 +315,13 @@
         <v>28</v>
       </c>
       <c r="D7" s="0">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="0">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -334,13 +335,13 @@
         <v>29</v>
       </c>
       <c r="D8" s="0">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="0">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -354,13 +355,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="0">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="0">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -374,13 +375,13 @@
         <v>31</v>
       </c>
       <c r="D10" s="0">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -394,13 +395,13 @@
         <v>32</v>
       </c>
       <c r="D11" s="0">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>36</v>
       </c>
       <c r="F11" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_wmprob.vois.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_wmprob.vois.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
